--- a/results/mi355x_dsr_mxfp4/mi355x_dsr_mxfp4_mtp0_ep1_tp8_profiling/prefill_breakdown.xlsx
+++ b/results/mi355x_dsr_mxfp4/mi355x_dsr_mxfp4_mtp0_ep1_tp8_profiling/prefill_breakdown.xlsx
@@ -471,22 +471,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>70.84</v>
+        <v>253.28</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>83.35900000000001</v>
+        <v>265.96</v>
       </c>
       <c r="F2" t="n">
-        <v>13.9</v>
+        <v>26.2</v>
       </c>
       <c r="G2" t="n">
-        <v>68.89657142857143</v>
+        <v>220.221380952381</v>
       </c>
       <c r="H2" t="n">
-        <v>81.56638095238095</v>
+        <v>232.8357142857143</v>
       </c>
     </row>
     <row r="3">
@@ -496,13 +496,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.519</v>
+        <v>12.68</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>12.66980952380952</v>
+        <v>12.61433333333333</v>
       </c>
     </row>
     <row r="4">
@@ -520,19 +520,19 @@
         <v>6.039</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="n">
         <v>6.039</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>5.987666666666667</v>
+        <v>5.978095238095237</v>
       </c>
       <c r="H4" t="n">
-        <v>5.987666666666667</v>
+        <v>5.978095238095237</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.199</v>
+        <v>30.519</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>30.199</v>
+        <v>30.519</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>30.23914285714286</v>
+        <v>30.60871428571429</v>
       </c>
       <c r="H5" t="n">
-        <v>30.23914285714286</v>
+        <v>30.60871428571429</v>
       </c>
     </row>
     <row r="6">
@@ -577,22 +577,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.039</v>
+        <v>5.199</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>5.039</v>
+        <v>5.199</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.764714285714286</v>
+        <v>5.317095238095238</v>
       </c>
       <c r="H6" t="n">
-        <v>4.764714285714286</v>
+        <v>5.317095238095238</v>
       </c>
     </row>
     <row r="7">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.319</v>
+        <v>12.399</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>12.319</v>
+        <v>12.399</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>12.50757142857143</v>
+        <v>12.52480952380952</v>
       </c>
       <c r="H7" t="n">
-        <v>12.50757142857143</v>
+        <v>12.52480952380952</v>
       </c>
     </row>
     <row r="8">
@@ -637,22 +637,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.319</v>
+        <v>5.839</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
-        <v>5.319</v>
+        <v>5.839</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G8" t="n">
-        <v>5.414238095238095</v>
+        <v>5.745809523809524</v>
       </c>
       <c r="H8" t="n">
-        <v>5.414238095238095</v>
+        <v>5.745809523809524</v>
       </c>
     </row>
     <row r="9">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.599</v>
+        <v>4.559</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>3.599</v>
+        <v>4.559</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G9" t="n">
-        <v>4.00852380952381</v>
+        <v>4.627571428571429</v>
       </c>
       <c r="H9" t="n">
-        <v>4.00852380952381</v>
+        <v>4.627571428571429</v>
       </c>
     </row>
     <row r="10">
@@ -697,22 +697,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.359</v>
+        <v>4.159</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>3.359</v>
+        <v>4.159</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G10" t="n">
-        <v>3.233333333333333</v>
+        <v>4.362809523809524</v>
       </c>
       <c r="H10" t="n">
-        <v>3.233333333333333</v>
+        <v>4.362809523809524</v>
       </c>
     </row>
     <row r="11">
@@ -727,22 +727,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.959</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="E11" t="n">
-        <v>8.959</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>8.926714285714286</v>
+        <v>8.738095238095237</v>
       </c>
       <c r="H11" t="n">
-        <v>8.926714285714286</v>
+        <v>8.738095238095237</v>
       </c>
     </row>
     <row r="12">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.599</v>
+        <v>9.839</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>10.599</v>
+        <v>9.839</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>10.35328571428571</v>
+        <v>9.896190476190476</v>
       </c>
       <c r="H12" t="n">
-        <v>10.35328571428571</v>
+        <v>9.896190476190476</v>
       </c>
     </row>
     <row r="13">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.279</v>
+        <v>25.919</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="E13" t="n">
-        <v>25.279</v>
+        <v>25.919</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>25.18947619047619</v>
+        <v>25.96671428571429</v>
       </c>
       <c r="H13" t="n">
-        <v>25.18947619047619</v>
+        <v>25.96671428571429</v>
       </c>
     </row>
     <row r="14">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.959</v>
+        <v>4.319</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>3.959</v>
+        <v>4.319</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="G14" t="n">
-        <v>3.957142857142857</v>
+        <v>4.471428571428572</v>
       </c>
       <c r="H14" t="n">
-        <v>3.957142857142857</v>
+        <v>4.471428571428572</v>
       </c>
     </row>
     <row r="15">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.759</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="E15" t="n">
-        <v>22.759</v>
+        <v>22.8</v>
       </c>
       <c r="F15" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>22.93080952380953</v>
+        <v>22.56876190476191</v>
       </c>
       <c r="H15" t="n">
-        <v>22.93080952380953</v>
+        <v>22.56876190476191</v>
       </c>
     </row>
     <row r="16">
@@ -877,22 +877,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68.36</v>
+        <v>295.841</v>
       </c>
       <c r="D16" t="n">
-        <v>11.4</v>
+        <v>29.2</v>
       </c>
       <c r="E16" t="n">
-        <v>78.999</v>
+        <v>307.24</v>
       </c>
       <c r="F16" t="n">
-        <v>13.1</v>
+        <v>30.3</v>
       </c>
       <c r="G16" t="n">
-        <v>68.73704761904762</v>
+        <v>290.8047142857143</v>
       </c>
       <c r="H16" t="n">
-        <v>79.73038095238095</v>
+        <v>301.9733333333334</v>
       </c>
     </row>
     <row r="17">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10.639</v>
+        <v>11.399</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>10.99333333333333</v>
+        <v>11.16861904761905</v>
       </c>
     </row>
     <row r="18">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.719</v>
+        <v>19.639</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="E18" t="n">
-        <v>19.719</v>
+        <v>19.639</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>19.4752380952381</v>
+        <v>20.19342857142857</v>
       </c>
       <c r="H18" t="n">
-        <v>19.4752380952381</v>
+        <v>20.19342857142857</v>
       </c>
     </row>
     <row r="19">
@@ -953,22 +953,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.479</v>
+        <v>4.239</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E19" t="n">
-        <v>281.954</v>
+        <v>281.395</v>
       </c>
       <c r="F19" t="n">
-        <v>46.9</v>
+        <v>27.7</v>
       </c>
       <c r="G19" t="n">
-        <v>4.559</v>
+        <v>4.431428571428571</v>
       </c>
       <c r="H19" t="n">
-        <v>277.938</v>
+        <v>280.2425714285714</v>
       </c>
     </row>
     <row r="20">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.279</v>
+        <v>4.959</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6.561095238095238</v>
+        <v>5.119047619047619</v>
       </c>
     </row>
     <row r="21">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.879</v>
+        <v>9.919</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>9.374285714285715</v>
+        <v>9.926714285714286</v>
       </c>
     </row>
     <row r="22">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.079</v>
+        <v>22.919</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>24.54757142857143</v>
+        <v>23.13433333333333</v>
       </c>
     </row>
     <row r="23">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>119.479</v>
+        <v>119.72</v>
       </c>
       <c r="D23" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
       <c r="G23" t="n">
-        <v>112.3123333333333</v>
+        <v>116.1274285714286</v>
       </c>
     </row>
     <row r="24">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.439</v>
+        <v>6.119</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="G24" t="n">
-        <v>6.568523809523809</v>
+        <v>6.583761904761905</v>
       </c>
     </row>
     <row r="25">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>111.32</v>
+        <v>113.52</v>
       </c>
       <c r="D25" t="n">
-        <v>18.5</v>
+        <v>11.2</v>
       </c>
       <c r="G25" t="n">
-        <v>114.0151904761905</v>
+        <v>114.9198571428571</v>
       </c>
     </row>
     <row r="26">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>601.4589999999999</v>
+        <v>1014.463</v>
       </c>
       <c r="D26" t="n">
         <v>100</v>
@@ -1085,7 +1085,7 @@
         <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>596.2226190476191</v>
+        <v>976.0511428571428</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1154,13 +1154,13 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>139.2</v>
+        <v>549.121</v>
       </c>
       <c r="D2" t="n">
-        <v>69.59999999999999</v>
+        <v>274.56</v>
       </c>
       <c r="E2" t="n">
-        <v>23.1</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="3">
@@ -1173,13 +1173,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>119.479</v>
+        <v>119.72</v>
       </c>
       <c r="D3" t="n">
-        <v>119.479</v>
+        <v>119.72</v>
       </c>
       <c r="E3" t="n">
-        <v>19.9</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="4">
@@ -1192,51 +1192,51 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>111.32</v>
+        <v>113.52</v>
       </c>
       <c r="D4" t="n">
-        <v>111.32</v>
+        <v>113.52</v>
       </c>
       <c r="E4" t="n">
-        <v>18.5</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>_fused_dynamic_mxfp4_quant_moe_sort_kernel</t>
+          <t>void ck_tile::kentry&lt;4, ck_tile::FlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;80, 64, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 128&gt;, false, false&gt;, 8, 4&gt;, ck_tile::FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::FlatmmPipelineProblem&lt;_BitInt(8), _BitInt(8), float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;80, 64, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 128&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)0, false, _BitInt(8)&gt;, ck_tile::UniversalFlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;_BitInt(8), _BitInt(8), ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 80, 64, 1, 4, 16, 16, 128, false, 1, false, 1, false, 1, false&gt;, void&gt;&gt;, ck_tile::FlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, 0&gt;&gt;(ck_tile::FlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, 0&gt;)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>30.518</v>
+        <v>30.519</v>
       </c>
       <c r="D5" t="n">
-        <v>15.259</v>
+        <v>30.519</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>void ck_tile::kentry&lt;4, ck_tile::FlatmmKernel&lt;ck_tile::GemmSpatiallyLocalTilePartitioner&lt;ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;80, 64, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 128&gt;, false, false&gt;, 8, 4&gt;, ck_tile::FlatmmPipelineAGmemBGmemCRegV1&lt;ck_tile::FlatmmPipelineProblem&lt;_BitInt(8), _BitInt(8), float, ck_tile::TileGemmShape&lt;ck_tile::sequence&lt;80, 64, 256&gt;, ck_tile::sequence&lt;1, 4, 1&gt;, ck_tile::sequence&lt;16, 16, 128&gt;, false, false&gt;, ck_tile::TileGemmUniversalTraits&lt;false, false, false, false, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::tensor_layout::gemm::ColumnMajor, ck_tile::tensor_layout::gemm::RowMajor, false, false, false, 1, true, 16&gt;, (ck_tile::GemmPipelineScheduler)0, true, (ck_tile::TailNumber)1, (ck_tile::amd_buffer_coherence_enum)0, false, _BitInt(8)&gt;, ck_tile::UniversalFlatmmPipelineAgBgCrPolicy&gt;, ck_tile::CShuffleEpilogue&lt;ck_tile::CShuffleEpilogueProblem&lt;_BitInt(8), _BitInt(8), ck_tile::tuple&lt;&gt;, float, std::bfloat16_t, ck_tile::tuple&lt;&gt;, ck_tile::tensor_layout::gemm::RowMajor, ck_tile::element_wise::PassThrough, 80, 64, 1, 4, 16, 16, 128, false, 1, false, 1, false, 1, false&gt;, void&gt;&gt;, ck_tile::FlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, 0&gt;&gt;(ck_tile::FlatmmKernelArgs&lt;ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, ck_tile::FlatmmScalePointer&lt;1, 0, float&gt;, 0&gt;)</t>
+          <t>_fused_dynamic_mxfp4_quant_moe_sort_kernel</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>30.199</v>
+        <v>29.038</v>
       </c>
       <c r="D6" t="n">
-        <v>30.199</v>
+        <v>14.519</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -1249,13 +1249,13 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>25.279</v>
+        <v>25.919</v>
       </c>
       <c r="D7" t="n">
-        <v>25.279</v>
+        <v>25.919</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1268,13 +1268,13 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>23.158</v>
+        <v>24.079</v>
       </c>
       <c r="D8" t="n">
-        <v>11.579</v>
+        <v>12.04</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -1287,13 +1287,13 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>22.759</v>
+        <v>22.8</v>
       </c>
       <c r="D9" t="n">
-        <v>22.759</v>
+        <v>22.8</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -1306,13 +1306,13 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>19.719</v>
+        <v>19.639</v>
       </c>
       <c r="D10" t="n">
-        <v>19.719</v>
+        <v>19.639</v>
       </c>
       <c r="E10" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -1325,51 +1325,51 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>12.319</v>
+        <v>12.399</v>
       </c>
       <c r="D11" t="n">
-        <v>12.319</v>
+        <v>12.399</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 16, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 16, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 16, false, false, true&gt; &gt;::Kargs)</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>10.599</v>
+        <v>9.919</v>
       </c>
       <c r="D12" t="n">
-        <v>10.599</v>
+        <v>9.919</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 16, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 16, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P23&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 16, false, false, true&gt; &gt;::Kargs)</t>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>9.879</v>
+        <v>9.839</v>
       </c>
       <c r="D13" t="n">
-        <v>9.879</v>
+        <v>9.839</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1382,13 +1382,13 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>8.959</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>8.959</v>
+        <v>8.638999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
@@ -1401,127 +1401,127 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>7.318</v>
+        <v>8.478</v>
       </c>
       <c r="D15" t="n">
-        <v>3.659</v>
+        <v>4.239</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 4, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 4, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 4, false, false, true&gt; &gt;::Kargs)</t>
+          <t>void aiter::dynamic_per_token_scaled_quant_kernel&lt;std::bfloat16_t, _BitInt(8), 32&gt;(_BitInt(8)*, float*, std::bfloat16_t*, float const*, int, int const*, int)</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>6.279</v>
+        <v>6.039</v>
       </c>
       <c r="D16" t="n">
-        <v>6.279</v>
+        <v>6.039</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>void aiter::dynamic_per_token_scaled_quant_kernel&lt;std::bfloat16_t, _BitInt(8), 32&gt;(_BitInt(8)*, float*, std::bfloat16_t*, float const*, int, int const*, int)</t>
+          <t>void aiter::kn_entry_2c_sbhd_cached_indirect_inplace&lt;aiter::OpCachedFwd, 1, true, false, true, true, c10::BFloat16, c10::BFloat16&gt;(c10::BFloat16*, c10::BFloat16*, c10::BFloat16 const*, c10::BFloat16 const*, long const*, int, int, int, int, int, int, int, int, int, int, int, int, int)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>6.039</v>
+        <v>5.839</v>
       </c>
       <c r="D17" t="n">
-        <v>6.039</v>
+        <v>5.839</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>void aiter::kn_entry_2c_sbhd_cached_indirect_inplace&lt;aiter::OpCachedFwd, 1, true, false, true, true, c10::BFloat16, c10::BFloat16&gt;(c10::BFloat16*, c10::BFloat16*, c10::BFloat16 const*, c10::BFloat16 const*, long const*, int, int, int, int, int, int, int, int, int, int, int, int, int)</t>
+          <t>_fused_rms_fp8_group_quant_kernel</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>5.319</v>
+        <v>5.199</v>
       </c>
       <c r="D18" t="n">
-        <v>5.319</v>
+        <v>5.199</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>_fused_rms_fp8_group_quant_kernel</t>
+          <t>void ck_tile::kentry&lt;2, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 4, false, false, true&gt; &gt;, ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 4, false, false, true&gt; &gt;::Kargs&gt;(ck_tile::MoeSortingMultiPhaseKernel_P0_v2&lt;ck_tile::MoeSortingProblemMp&lt;int, float, unsigned char, 4, false, false, true&gt; &gt;::Kargs)</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>5.039</v>
+        <v>4.959</v>
       </c>
       <c r="D19" t="n">
-        <v>5.039</v>
+        <v>4.959</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>void aiter::grouped_topk_opt_sort_kernel&lt;c10::BFloat16, float __vector(4), 8, true, true, false&gt;(c10::BFloat16*, c10::BFloat16 const*, float*, int*, unsigned long, int, int, int, int, float)</t>
+          <t>void aiter::concat_and_cache_mla_opt_kernel&lt;std::bfloat16_t, _BitInt(8), (vllm::Fp8KVCacheDataType)1&gt;(std::bfloat16_t const*, std::bfloat16_t const*, _BitInt(8)*, long const*, int, int, int, int, int, int, int, float const*)</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>4.479</v>
+        <v>4.559</v>
       </c>
       <c r="D20" t="n">
-        <v>4.479</v>
+        <v>4.559</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>void aiter::concat_and_cache_mla_opt_kernel&lt;std::bfloat16_t, _BitInt(8), (vllm::Fp8KVCacheDataType)1&gt;(std::bfloat16_t const*, std::bfloat16_t const*, _BitInt(8)*, long const*, int, int, int, int, int, int, int, float const*)</t>
+          <t>void aiter::grouped_topk_opt_sort_kernel&lt;c10::BFloat16, float __vector(4), 8, true, true, false&gt;(c10::BFloat16*, c10::BFloat16 const*, float*, int*, unsigned long, int, int, int, int, float)</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>3.599</v>
+        <v>4.239</v>
       </c>
       <c r="D21" t="n">
-        <v>3.599</v>
+        <v>4.239</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
